--- a/Bangalore-November-2025.xlsx
+++ b/Bangalore-November-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="88">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Bangalore</t>
   </si>
   <si>
@@ -208,10 +211,10 @@
     <t>KA03AK7732</t>
   </si>
   <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Crysta</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -223,13 +226,13 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>Celerio</t>
-  </si>
-  <si>
-    <t>MG EVS</t>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CELERIO</t>
+  </si>
+  <si>
+    <t>MG ZS EV</t>
   </si>
   <si>
     <t>28/02/2024</t>
@@ -259,9 +262,6 @@
     <t>19/11/2019</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>23/03/2023</t>
   </si>
   <si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>30/07/2024</t>
+  </si>
+  <si>
+    <t>23/03/2021</t>
   </si>
   <si>
     <t>13/11/2025</t>
@@ -636,10 +639,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,25 +721,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="2">
         <v>45174</v>
@@ -799,27 +805,27 @@
         <v>20.58</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H3">
         <v>57441</v>
@@ -879,27 +885,27 @@
         <v>38.28</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4">
         <v>75122</v>
@@ -959,24 +965,24 @@
         <v>40.23</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2">
         <v>43560</v>
@@ -1039,27 +1045,27 @@
         <v>63.28</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>178369</v>
@@ -1119,27 +1125,27 @@
         <v>39.7</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7">
         <v>124950</v>
@@ -1199,27 +1205,27 @@
         <v>54.78</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8">
         <v>88729</v>
@@ -1279,24 +1285,24 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2">
         <v>44387</v>
@@ -1359,27 +1365,27 @@
         <v>42.07</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>80778</v>
@@ -1439,24 +1445,24 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2">
         <v>44257</v>
@@ -1519,24 +1525,24 @@
         <v>29.17</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2">
         <v>44387</v>
@@ -1599,24 +1605,24 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2">
         <v>45634</v>
@@ -1679,24 +1685,24 @@
         <v>8.01</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2">
         <v>45147</v>
@@ -1759,24 +1765,24 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2">
         <v>44746</v>
@@ -1839,27 +1845,27 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16">
         <v>67765</v>
@@ -1924,22 +1930,22 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17">
         <v>62657</v>
@@ -2004,19 +2010,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2">
         <v>44629</v>
@@ -2084,22 +2090,22 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19">
         <v>23594</v>
@@ -2164,19 +2170,19 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2">
         <v>44629</v>
@@ -2244,22 +2250,22 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H21">
         <v>65302</v>
@@ -2324,22 +2330,22 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" t="s">
-        <v>81</v>
+        <v>66</v>
+      </c>
+      <c r="G22" s="2">
+        <v>44350</v>
       </c>
       <c r="H22">
         <v>86232</v>
@@ -2404,19 +2410,19 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
         <v>82</v>
@@ -2484,19 +2490,19 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>
@@ -2564,19 +2570,19 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
         <v>83</v>
@@ -2644,19 +2650,19 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2">
         <v>45174</v>
@@ -2724,19 +2730,19 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2">
         <v>45235</v>
@@ -2804,19 +2810,19 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
         <v>84</v>
@@ -2884,19 +2890,19 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2">
         <v>45174</v>
@@ -2964,19 +2970,19 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
         <v>85</v>
@@ -3044,22 +3050,22 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H31">
         <v>93408</v>
@@ -3124,19 +3130,19 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G32" s="2">
         <v>44628</v>
@@ -3204,19 +3210,19 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G33" s="2">
         <v>45849</v>
@@ -3284,19 +3290,19 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G34" s="2">
         <v>45849</v>
@@ -3364,19 +3370,19 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G35" s="2">
         <v>45849</v>
@@ -3444,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H36">
         <v>181</v>
@@ -3524,19 +3530,19 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
         <v>82</v>
